--- a/HH Realty Tracker V14.xlsx
+++ b/HH Realty Tracker V14.xlsx
@@ -15,7 +15,9 @@
     <sheet name="📋 Instructions" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="⚙️ Lookups" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="AgentNameList">'👤 Agents'!$C$4:$C$38</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -814,7 +816,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblAgent" displayName="tblAgent" ref="C3:D38" headerRowCount="1">
   <autoFilter ref="C3:D38"/>
   <tableColumns count="2">
-    <tableColumn id="3" name="Agent Name"/>
+    <tableColumn id="3" name="AgentName"/>
     <tableColumn id="4" name="Office"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
@@ -2091,33 +2093,30 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B13:F13"/>
   </mergeCells>
-  <dataValidations count="9">
+  <dataValidations count="8">
     <dataValidation sqref="C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=tblLoanType[LoanType]</formula1>
+      <formula1>"CONV,FHA,VA,CASH,New Const,Eq. Ln,Other"</formula1>
     </dataValidation>
     <dataValidation sqref="C14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=tblAgent[AgentName]</formula1>
+      <formula1>AgentNameList</formula1>
     </dataValidation>
     <dataValidation sqref="F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=tblAgent[AgentName]</formula1>
+      <formula1>AgentNameList</formula1>
     </dataValidation>
     <dataValidation sqref="C17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=tblYN[YN]</formula1>
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=tblEMHold[EMHold]</formula1>
+      <formula1>"HH,Title,CoBroke,Buyer,Seller,N/A,Other"</formula1>
     </dataValidation>
     <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=tblYN[YN]</formula1>
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=tblHWPay[HWPay]</formula1>
+      <formula1>"Seller,Buyer,Split,Other,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=tblYN[YN]</formula1>
-    </dataValidation>
-    <dataValidation sqref="C17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=tblYN[YN]</formula1>
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2457,11 +2456,11 @@
         </is>
       </c>
       <c r="Z5" s="58">
-        <f>IFERROR(VLOOKUP(K5,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K5,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA5" s="58">
-        <f>IFERROR(VLOOKUP(L5,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L5,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB5" s="59">
@@ -2570,11 +2569,11 @@
         </is>
       </c>
       <c r="Z6" s="58">
-        <f>IFERROR(VLOOKUP(K6,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K6,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA6" s="58">
-        <f>IFERROR(VLOOKUP(L6,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L6,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB6" s="59">
@@ -2681,11 +2680,11 @@
         </is>
       </c>
       <c r="Z7" s="58">
-        <f>IFERROR(VLOOKUP(K7,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K7,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA7" s="58">
-        <f>IFERROR(VLOOKUP(L7,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L7,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB7" s="59">
@@ -2792,11 +2791,11 @@
         </is>
       </c>
       <c r="Z8" s="58">
-        <f>IFERROR(VLOOKUP(K8,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K8,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA8" s="58">
-        <f>IFERROR(VLOOKUP(L8,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L8,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB8" s="59">
@@ -2903,11 +2902,11 @@
         </is>
       </c>
       <c r="Z9" s="58">
-        <f>IFERROR(VLOOKUP(K9,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K9,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA9" s="58">
-        <f>IFERROR(VLOOKUP(L9,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L9,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB9" s="59">
@@ -3016,11 +3015,11 @@
         </is>
       </c>
       <c r="Z10" s="58">
-        <f>IFERROR(VLOOKUP(K10,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K10,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA10" s="58">
-        <f>IFERROR(VLOOKUP(L10,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L10,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB10" s="59">
@@ -3129,11 +3128,11 @@
         </is>
       </c>
       <c r="Z11" s="58">
-        <f>IFERROR(VLOOKUP(K11,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K11,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA11" s="58">
-        <f>IFERROR(VLOOKUP(L11,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L11,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB11" s="59">
@@ -3240,11 +3239,11 @@
         </is>
       </c>
       <c r="Z12" s="58">
-        <f>IFERROR(VLOOKUP(K12,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K12,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA12" s="58">
-        <f>IFERROR(VLOOKUP(L12,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L12,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB12" s="59">
@@ -3351,11 +3350,11 @@
         </is>
       </c>
       <c r="Z13" s="58">
-        <f>IFERROR(VLOOKUP(K13,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K13,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA13" s="58">
-        <f>IFERROR(VLOOKUP(L13,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L13,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB13" s="59">
@@ -3462,11 +3461,11 @@
         </is>
       </c>
       <c r="Z14" s="58">
-        <f>IFERROR(VLOOKUP(K14,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K14,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA14" s="58">
-        <f>IFERROR(VLOOKUP(L14,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L14,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB14" s="59">
@@ -3573,11 +3572,11 @@
         </is>
       </c>
       <c r="Z15" s="58">
-        <f>IFERROR(VLOOKUP(K15,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K15,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA15" s="58">
-        <f>IFERROR(VLOOKUP(L15,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L15,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB15" s="59">
@@ -3684,11 +3683,11 @@
         </is>
       </c>
       <c r="Z16" s="58">
-        <f>IFERROR(VLOOKUP(K16,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K16,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA16" s="58">
-        <f>IFERROR(VLOOKUP(L16,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L16,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB16" s="59">
@@ -3797,11 +3796,11 @@
         </is>
       </c>
       <c r="Z17" s="58">
-        <f>IFERROR(VLOOKUP(K17,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K17,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA17" s="58">
-        <f>IFERROR(VLOOKUP(L17,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L17,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB17" s="59">
@@ -3908,11 +3907,11 @@
         </is>
       </c>
       <c r="Z18" s="58">
-        <f>IFERROR(VLOOKUP(K18,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K18,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA18" s="58">
-        <f>IFERROR(VLOOKUP(L18,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L18,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB18" s="59">
@@ -4019,11 +4018,11 @@
         </is>
       </c>
       <c r="Z19" s="58">
-        <f>IFERROR(VLOOKUP(K19,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K19,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA19" s="58">
-        <f>IFERROR(VLOOKUP(L19,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L19,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB19" s="59">
@@ -4132,11 +4131,11 @@
         </is>
       </c>
       <c r="Z20" s="58">
-        <f>IFERROR(VLOOKUP(K20,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K20,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA20" s="58">
-        <f>IFERROR(VLOOKUP(L20,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L20,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB20" s="59">
@@ -4243,11 +4242,11 @@
         </is>
       </c>
       <c r="Z21" s="58">
-        <f>IFERROR(VLOOKUP(K21,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K21,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA21" s="58">
-        <f>IFERROR(VLOOKUP(L21,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L21,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB21" s="59">
@@ -4356,11 +4355,11 @@
         </is>
       </c>
       <c r="Z22" s="58">
-        <f>IFERROR(VLOOKUP(K22,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K22,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA22" s="58">
-        <f>IFERROR(VLOOKUP(L22,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L22,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB22" s="59">
@@ -4487,11 +4486,11 @@
         </is>
       </c>
       <c r="Z23" s="58">
-        <f>IFERROR(VLOOKUP(K23,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K23,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA23" s="58">
-        <f>IFERROR(VLOOKUP(L23,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L23,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB23" s="59">
@@ -4620,11 +4619,11 @@
         </is>
       </c>
       <c r="Z24" s="58">
-        <f>IFERROR(VLOOKUP(K24,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K24,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA24" s="58">
-        <f>IFERROR(VLOOKUP(L24,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L24,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB24" s="59">
@@ -4757,11 +4756,11 @@
         </is>
       </c>
       <c r="Z25" s="58">
-        <f>IFERROR(VLOOKUP(K25,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K25,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA25" s="58">
-        <f>IFERROR(VLOOKUP(L25,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L25,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB25" s="59">
@@ -4896,11 +4895,11 @@
         </is>
       </c>
       <c r="Z26" s="58">
-        <f>IFERROR(VLOOKUP(K26,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K26,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA26" s="58">
-        <f>IFERROR(VLOOKUP(L26,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L26,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB26" s="59">
@@ -5035,11 +5034,11 @@
         </is>
       </c>
       <c r="Z27" s="58">
-        <f>IFERROR(VLOOKUP(K27,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K27,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA27" s="58">
-        <f>IFERROR(VLOOKUP(L27,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L27,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB27" s="59">
@@ -5172,11 +5171,11 @@
         </is>
       </c>
       <c r="Z28" s="58">
-        <f>IFERROR(VLOOKUP(K28,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(K28,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AA28" s="58">
-        <f>IFERROR(VLOOKUP(L28,tblAgent[#All],2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(L28,'👤 Agents'!$C$4:$D$200,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="AB28" s="59">
@@ -5246,31 +5245,31 @@
   </conditionalFormatting>
   <dataValidations count="11">
     <dataValidation sqref="I5:I200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Invalid value. Use the dropdown." type="list">
-      <formula1>=tblLoanType[LoanType]</formula1>
+      <formula1>"CONV,FHA,VA,CASH,New Const,Eq. Ln,Other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q5:Q200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Invalid value. Use the dropdown." type="list">
+      <formula1>"HH,Title,CoBroke,Buyer,Seller,N/A,Other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R5:R200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Invalid value. Use the dropdown." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="S5:S200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Invalid value. Use the dropdown." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="T5:T200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Invalid value. Use the dropdown." type="list">
+      <formula1>"Seller,Buyer,Split,Other,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="U5:U200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Invalid value. Use the dropdown." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y5:Y200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Invalid value. Use the dropdown." type="list">
+      <formula1>"Active,Closed,BOMB"</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Invalid value. Use the dropdown." type="list">
-      <formula1>=tblAgent[AgentName]</formula1>
+      <formula1>AgentNameList</formula1>
     </dataValidation>
     <dataValidation sqref="L5:L200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Invalid value. Use the dropdown." type="list">
-      <formula1>=tblAgent[AgentName]</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q5:Q200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Invalid value. Use the dropdown." type="list">
-      <formula1>=tblEMHold[EMHold]</formula1>
-    </dataValidation>
-    <dataValidation sqref="R5:R200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Invalid value. Use the dropdown." type="list">
-      <formula1>=tblYN[YN]</formula1>
-    </dataValidation>
-    <dataValidation sqref="S5:S200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Invalid value. Use the dropdown." type="list">
-      <formula1>=tblYN[YN]</formula1>
-    </dataValidation>
-    <dataValidation sqref="T5:T200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Invalid value. Use the dropdown." type="list">
-      <formula1>=tblHWPay[HWPay]</formula1>
-    </dataValidation>
-    <dataValidation sqref="U5:U200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Invalid value. Use the dropdown." type="list">
-      <formula1>=tblYN[YN]</formula1>
-    </dataValidation>
-    <dataValidation sqref="Y5:Y200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Entry" error="Invalid value. Use the dropdown." type="list">
-      <formula1>=tblTransStatus[TransStatus]</formula1>
+      <formula1>AgentNameList</formula1>
     </dataValidation>
     <dataValidation sqref="G5:H200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Date" error="Please enter a valid date (mm/dd/yyyy)." type="date" operator="greaterThan">
       <formula1>DATE(2000,1,1)</formula1>
@@ -11439,7 +11438,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="C5:AV200" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Status" error="Choose: Not Started, In Progress, Waiting, Complete, or N/A" promptTitle="Select Status" prompt="Choose the status for this checklist item." type="list">
-      <formula1>=tblStatus[Status]</formula1>
+      <formula1>"Not Started,In Progress,Waiting,Complete,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11490,7 +11489,7 @@
       </c>
       <c r="C3" s="79" t="inlineStr">
         <is>
-          <t>Agent Name</t>
+          <t>AgentName</t>
         </is>
       </c>
       <c r="D3" s="79" t="inlineStr">
